--- a/output/isabel-cohorts/이서연반_총점_성장.xlsx
+++ b/output/isabel-cohorts/이서연반_총점_성장.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <r>
       <rPr>
@@ -137,7 +137,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1 75.5</t>
+      <t xml:space="preserve">1 75.3</t>
     </r>
     <r>
       <rPr>
@@ -154,7 +154,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2 82.0</t>
+      <t xml:space="preserve">2 81.2</t>
     </r>
     <r>
       <rPr>
@@ -224,7 +224,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">65.6</t>
+      <t xml:space="preserve">65.0</t>
     </r>
     <r>
       <rPr>
@@ -258,7 +258,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+16.4</t>
+      <t xml:space="preserve">+16.2</t>
     </r>
     <r>
       <rPr>
@@ -294,6 +294,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">5</t>
     </r>
     <r>
@@ -302,23 +319,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">명 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">명</t>
     </r>
     <r>
@@ -353,6 +353,110 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">이서연</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">황재성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서예준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이시원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 그룹이 올라갈 때마다 평균 점수도 올랐습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 나머지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">김채율</t>
     </r>
     <r>
@@ -362,66 +466,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이서연</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">황재성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서예준</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 그룹이 올라갈 때마다 평균 점수도 올랐습니다</t>
+      <t xml:space="preserve">(76.5 → 76.0) — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그룹 안에서 시험마다 점수 차이가 큰 학생입니다</t>
     </r>
     <r>
       <rPr>
@@ -601,6 +654,9 @@
     <t xml:space="preserve">서예준</t>
   </si>
   <si>
+    <t xml:space="preserve">이시원</t>
+  </si>
+  <si>
     <t xml:space="preserve">반 평균</t>
   </si>
   <si>
@@ -945,7 +1001,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -980,6 +1036,159 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 4</t>
     </r>
     <r>
       <rPr>
@@ -1151,7 +1360,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">65.6</t>
+      <t xml:space="preserve">65.0</t>
     </r>
     <r>
       <rPr>
@@ -1168,7 +1377,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">80.8</t>
+      <t xml:space="preserve">79.2</t>
     </r>
     <r>
       <rPr>
@@ -1185,7 +1394,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(+15.2</t>
+      <t xml:space="preserve">(+14.2</t>
     </r>
     <r>
       <rPr>
@@ -1289,6 +1498,40 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2</t>
     </r>
     <r>
@@ -1297,6 +1540,40 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">명 → 마지막 시험 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">명</t>
     </r>
     <r>
@@ -1306,7 +1583,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, 5</t>
+      <t xml:space="preserve">, 2</t>
     </r>
     <r>
       <rPr>
@@ -1323,23 +1600,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 → 마지막 시험 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">1</t>
     </r>
     <r>
@@ -1348,6 +1608,23 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">등급 </t>
     </r>
     <r>
@@ -1357,75 +1634,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">4</t>
     </r>
     <r>
       <rPr>
@@ -1542,6 +1751,186 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 4</t>
     </r>
     <r>
       <rPr>
@@ -2062,7 +2451,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">82.0</t>
+      <t xml:space="preserve">81.2</t>
     </r>
     <r>
       <rPr>
@@ -2181,7 +2570,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -2301,41 +2690,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모의고사 첫 시험보다 반 평균이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점 이상 높습니다</t>
+      <t xml:space="preserve">이서연 반은 현재 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라 고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사는 아직 보지 않았습니다</t>
     </r>
     <r>
       <rPr>
@@ -2708,12 +3097,12 @@
       <rgbColor rgb="FF1E7A72"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF878787"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFBE4B48"/>
+      <rgbColor rgb="FFA6B8B4"/>
+      <rgbColor rgb="FFAA433F"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFDB8238"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFC9D6D2"/>
       <rgbColor rgb="FF000080"/>
@@ -2722,7 +3111,7 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF3D97AF"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
@@ -2732,14 +3121,14 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF4A7EBB"/>
-      <rgbColor rgb="FF46AAC4"/>
-      <rgbColor rgb="FF98B855"/>
+      <rgbColor rgb="FF426FA6"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF7D5FA0"/>
-      <rgbColor rgb="FFA6B8B4"/>
+      <rgbColor rgb="FF6F568D"/>
+      <rgbColor rgb="FF87A44B"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF3E9A90"/>
       <rgbColor rgb="FF003300"/>
@@ -2842,7 +3231,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'총점 성장 요약'!$B$8:$D$8</c:f>
+              <c:f>'총점 성장 요약'!$B$9:$D$9</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2861,18 +3250,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'총점 성장 요약'!$B$14:$D$14</c:f>
+              <c:f>'총점 성장 요약'!$B$16:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>65.6</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75.5333333333333</c:v>
+                  <c:v>75.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>82</c:v>
+                  <c:v>81.1666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2880,11 +3269,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41037890"/>
-        <c:axId val="51768170"/>
+        <c:axId val="90456211"/>
+        <c:axId val="23811808"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41037890"/>
+        <c:axId val="90456211"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2916,7 +3305,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51768170"/>
+        <c:crossAx val="23811808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2924,7 +3313,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51768170"/>
+        <c:axId val="23811808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2968,7 +3357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41037890"/>
+        <c:crossAx val="90456211"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3046,7 +3435,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'총점 성장 요약'!B8</c:f>
+              <c:f>'총점 성장 요약'!B9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3096,9 +3485,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'총점 성장 요약'!$A$9:$A$13</c:f>
+              <c:f>'총점 성장 요약'!$A$10:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>김지수</c:v>
                 </c:pt>
@@ -3113,16 +3502,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>서예준</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>이시원</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'총점 성장 요약'!$B$9:$B$13</c:f>
+              <c:f>'총점 성장 요약'!$B$10:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>63</c:v>
                 </c:pt>
@@ -3137,6 +3529,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3147,7 +3542,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'총점 성장 요약'!C8</c:f>
+              <c:f>'총점 성장 요약'!C9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3198,9 +3593,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'총점 성장 요약'!$A$9:$A$13</c:f>
+              <c:f>'총점 성장 요약'!$A$10:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>김지수</c:v>
                 </c:pt>
@@ -3215,30 +3610,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>서예준</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>이시원</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'총점 성장 요약'!$C$9:$C$13</c:f>
+              <c:f>'총점 성장 요약'!$C$10:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>68</c:v>
+                  <c:v>66.6666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73</c:v>
+                  <c:v>76.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91.6666666666667</c:v>
+                  <c:v>92.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>76.3333333333333</c:v>
+                  <c:v>77.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>68.6666666666667</c:v>
+                  <c:v>69.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3249,7 +3650,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'총점 성장 요약'!D8</c:f>
+              <c:f>'총점 성장 요약'!D9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3300,9 +3701,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'총점 성장 요약'!$A$9:$A$13</c:f>
+              <c:f>'총점 성장 요약'!$A$10:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>김지수</c:v>
                 </c:pt>
@@ -3317,16 +3718,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>서예준</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>이시원</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'총점 성장 요약'!$D$9:$D$13</c:f>
+              <c:f>'총점 성장 요약'!$D$10:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>77</c:v>
                 </c:pt>
@@ -3341,6 +3745,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3348,11 +3755,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19316865"/>
-        <c:axId val="24730320"/>
+        <c:axId val="5857185"/>
+        <c:axId val="14135670"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19316865"/>
+        <c:axId val="5857185"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3384,7 +3791,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24730320"/>
+        <c:crossAx val="14135670"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3392,7 +3799,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24730320"/>
+        <c:axId val="14135670"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3436,7 +3843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19316865"/>
+        <c:crossAx val="5857185"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3548,11 +3955,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
+              <a:srgbClr val="426fa6"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="426fa6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3562,7 +3969,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="426fa6"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -3593,18 +4000,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차 (2025)
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차 (2026)
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차 (2026)
 고1</c:v>
                 </c:pt>
@@ -3613,17 +4032,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$9:$D$9</c:f>
+              <c:f>'고1 모의고사'!$B$9:$G$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>66</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3647,11 +4075,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="be4b48"/>
+              <a:srgbClr val="aa433f"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="aa433f"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3661,7 +4089,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="aa433f"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -3692,18 +4120,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차 (2025)
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차 (2026)
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차 (2026)
 고1</c:v>
                 </c:pt>
@@ -3712,17 +4152,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$10:$D$10</c:f>
+              <c:f>'고1 모의고사'!$B$10:$G$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>87</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>73</c:v>
                 </c:pt>
               </c:numCache>
@@ -3746,11 +4195,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="98b855"/>
+              <a:srgbClr val="87a44b"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="98b855"/>
+                <a:srgbClr val="87a44b"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3760,7 +4209,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="98b855"/>
+                <a:srgbClr val="87a44b"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -3791,18 +4240,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차 (2025)
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차 (2026)
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차 (2026)
 고1</c:v>
                 </c:pt>
@@ -3811,17 +4272,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$11:$D$11</c:f>
+              <c:f>'고1 모의고사'!$B$11:$G$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>87</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
@@ -3845,11 +4315,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="7d5fa0"/>
+              <a:srgbClr val="6f568d"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="7d5fa0"/>
+                <a:srgbClr val="6f568d"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3859,7 +4329,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7d5fa0"/>
+                <a:srgbClr val="6f568d"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -3890,18 +4360,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차 (2025)
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차 (2026)
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차 (2026)
 고1</c:v>
                 </c:pt>
@@ -3910,17 +4392,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$12:$D$12</c:f>
+              <c:f>'고1 모의고사'!$B$12:$G$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>88</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>74</c:v>
                 </c:pt>
               </c:numCache>
@@ -3944,11 +4435,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="46aac4"/>
+              <a:srgbClr val="3d97af"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="46aac4"/>
+                <a:srgbClr val="3d97af"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3958,7 +4449,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="46aac4"/>
+                <a:srgbClr val="3d97af"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -3989,18 +4480,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차 (2025)
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차 (2026)
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차 (2026)
 고1</c:v>
                 </c:pt>
@@ -4009,17 +4512,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$13:$D$13</c:f>
+              <c:f>'고1 모의고사'!$B$13:$G$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>73</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>82</c:v>
                 </c:pt>
               </c:numCache>
@@ -4033,6 +4545,126 @@
           <c:tx>
             <c:strRef>
               <c:f>'고1 모의고사'!A14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="db8238"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="db8238"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="db8238"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>중1 1차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>중2 1차 (2026)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>중2 2차 (2026)
+고1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고1 모의고사'!$B$14:$G$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>71</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고1 모의고사'!A15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4093,18 +4725,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차 (2025)
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차 (2025)
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차 (2026)
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차 (2026)
 고1</c:v>
                 </c:pt>
@@ -4113,18 +4757,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$14:$D$14</c:f>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>65.6</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>80.2</c:v>
+                  <c:v>73.1666666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>80.8</c:v>
+                  <c:v>73.8333333333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>81.3333333333333</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>79.1666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4139,11 +4792,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="38625054"/>
-        <c:axId val="44530694"/>
+        <c:axId val="67900880"/>
+        <c:axId val="73448983"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38625054"/>
+        <c:axId val="67900880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4175,7 +4828,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44530694"/>
+        <c:crossAx val="73448983"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4183,7 +4836,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44530694"/>
+        <c:axId val="73448983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4261,7 +4914,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38625054"/>
+        <c:crossAx val="67900880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -4364,7 +5017,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!E8</c:f>
+              <c:f>'고1 모의고사'!H8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4413,9 +5066,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$A$9:$A$14</c:f>
+              <c:f>'고1 모의고사'!$A$9:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>김지수</c:v>
                 </c:pt>
@@ -4432,6 +5085,9 @@
                   <c:v>서예준</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>이시원</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>반 평균</c:v>
                 </c:pt>
               </c:strCache>
@@ -4439,10 +5095,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$E$9:$E$14</c:f>
+              <c:f>'고1 모의고사'!$H$9:$H$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>63</c:v>
                 </c:pt>
@@ -4459,7 +5115,10 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>65.6</c:v>
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4470,7 +5129,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!F8</c:f>
+              <c:f>'고1 모의고사'!I8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4519,9 +5178,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$A$9:$A$14</c:f>
+              <c:f>'고1 모의고사'!$A$9:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>김지수</c:v>
                 </c:pt>
@@ -4538,6 +5197,9 @@
                   <c:v>서예준</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>이시원</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>반 평균</c:v>
                 </c:pt>
               </c:strCache>
@@ -4545,10 +5207,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$F$9:$F$14</c:f>
+              <c:f>'고1 모의고사'!$I$9:$I$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>75</c:v>
                 </c:pt>
@@ -4565,7 +5227,10 @@
                   <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80.8</c:v>
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>79.1666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4573,11 +5238,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94724924"/>
-        <c:axId val="32964650"/>
+        <c:axId val="24695097"/>
+        <c:axId val="44001125"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94724924"/>
+        <c:axId val="24695097"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4609,7 +5274,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32964650"/>
+        <c:crossAx val="44001125"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4617,7 +5282,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32964650"/>
+        <c:axId val="44001125"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4661,7 +5326,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94724924"/>
+        <c:crossAx val="24695097"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4773,11 +5438,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
+              <a:srgbClr val="426fa6"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="426fa6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4787,7 +5452,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="426fa6"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -4858,11 +5523,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="be4b48"/>
+              <a:srgbClr val="aa433f"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="aa433f"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4872,7 +5537,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="aa433f"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -4943,11 +5608,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="98b855"/>
+              <a:srgbClr val="87a44b"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="98b855"/>
+                <a:srgbClr val="87a44b"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4957,7 +5622,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="98b855"/>
+                <a:srgbClr val="87a44b"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -5028,11 +5693,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="7d5fa0"/>
+              <a:srgbClr val="6f568d"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="7d5fa0"/>
+                <a:srgbClr val="6f568d"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5042,7 +5707,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7d5fa0"/>
+                <a:srgbClr val="6f568d"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -5113,11 +5778,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="46aac4"/>
+              <a:srgbClr val="3d97af"/>
             </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="46aac4"/>
+                <a:srgbClr val="3d97af"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5127,7 +5792,7 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="46aac4"/>
+                <a:srgbClr val="3d97af"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -5188,6 +5853,91 @@
           <c:tx>
             <c:strRef>
               <c:f>'고2 모의고사'!A13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="db8238"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="db8238"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="db8238"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고2 모의고사'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중2 3차 (2026)
+고2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고2 모의고사'!$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>77</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고2 모의고사'!A14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5260,12 +6010,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$13</c:f>
+              <c:f>'고2 모의고사'!$B$14</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>82</c:v>
+                  <c:v>81.1666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5280,11 +6030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="8028404"/>
-        <c:axId val="32956970"/>
+        <c:axId val="86492067"/>
+        <c:axId val="68043246"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8028404"/>
+        <c:axId val="86492067"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5316,7 +6066,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32956970"/>
+        <c:crossAx val="68043246"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5324,7 +6074,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32956970"/>
+        <c:axId val="68043246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5402,7 +6152,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8028404"/>
+        <c:crossAx val="86492067"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -5461,13 +6211,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>134280</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1022040</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -5476,7 +6226,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3438360"/>
+        <a:off x="0" y="3857760"/>
         <a:ext cx="5039640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5491,13 +6241,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1193400</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -5506,7 +6256,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="7248600"/>
+        <a:off x="0" y="7667640"/>
         <a:ext cx="6479640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5526,13 +6276,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>134280</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>332280</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -5541,7 +6291,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3438360"/>
+        <a:off x="0" y="3857760"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5556,13 +6306,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>332280</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -5571,7 +6321,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="7248600"/>
+        <a:off x="0" y="7667640"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5591,13 +6341,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>134280</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>332280</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -5606,7 +6356,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3209760"/>
+        <a:off x="0" y="3400560"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5800,7 +6550,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5867,42 +6617,34 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <f aca="false">'고1 모의고사'!B9</f>
-        <v>63</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <f aca="false">'고1 모의고사'!H9</f>
-        <v>68</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <f aca="false">'고2 모의고사'!C8</f>
-        <v>77</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <f aca="false">D9-B9</f>
-        <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5910,20 +6652,20 @@
         <v>11</v>
       </c>
       <c r="B10" s="5" t="n">
-        <f aca="false">'고1 모의고사'!B10</f>
-        <v>59</v>
+        <f aca="false">'고1 모의고사'!B9</f>
+        <v>63</v>
       </c>
       <c r="C10" s="6" t="n">
-        <f aca="false">'고1 모의고사'!H10</f>
-        <v>73</v>
+        <f aca="false">'고1 모의고사'!K9</f>
+        <v>66.6666666666667</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">'고2 모의고사'!C9</f>
-        <v>76</v>
+        <f aca="false">'고2 모의고사'!C8</f>
+        <v>77</v>
       </c>
       <c r="E10" s="7" t="n">
         <f aca="false">D10-B10</f>
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5931,20 +6673,20 @@
         <v>12</v>
       </c>
       <c r="B11" s="5" t="n">
-        <f aca="false">'고1 모의고사'!B11</f>
-        <v>88</v>
+        <f aca="false">'고1 모의고사'!B10</f>
+        <v>59</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">'고1 모의고사'!H11</f>
-        <v>91.6666666666667</v>
+        <f aca="false">'고1 모의고사'!K10</f>
+        <v>76.5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">'고2 모의고사'!C10</f>
-        <v>95</v>
+        <f aca="false">'고2 모의고사'!C9</f>
+        <v>76</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">D11-B11</f>
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5952,20 +6694,20 @@
         <v>13</v>
       </c>
       <c r="B12" s="5" t="n">
-        <f aca="false">'고1 모의고사'!B12</f>
-        <v>67</v>
+        <f aca="false">'고1 모의고사'!B11</f>
+        <v>88</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">'고1 모의고사'!H12</f>
-        <v>76.3333333333333</v>
+        <f aca="false">'고1 모의고사'!K11</f>
+        <v>92.3333333333333</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">'고2 모의고사'!C11</f>
-        <v>82</v>
+        <f aca="false">'고2 모의고사'!C10</f>
+        <v>95</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">D12-B12</f>
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5973,54 +6715,97 @@
         <v>14</v>
       </c>
       <c r="B13" s="5" t="n">
+        <f aca="false">'고1 모의고사'!B12</f>
+        <v>67</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <f aca="false">'고1 모의고사'!K12</f>
+        <v>77.5</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <f aca="false">'고2 모의고사'!C11</f>
+        <v>82</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <f aca="false">D13-B13</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5" t="n">
         <f aca="false">'고1 모의고사'!B13</f>
         <v>51</v>
       </c>
-      <c r="C13" s="6" t="n">
-        <f aca="false">'고1 모의고사'!H13</f>
-        <v>68.6666666666667</v>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C14" s="6" t="n">
+        <f aca="false">'고1 모의고사'!K13</f>
+        <v>69.5</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <f aca="false">'고2 모의고사'!C12</f>
         <v>80</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <f aca="false">D13-B13</f>
+      <c r="E14" s="7" t="n">
+        <f aca="false">D14-B14</f>
         <v>29</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <f aca="false">'고1 모의고사'!B14</f>
+        <v>62</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <f aca="false">'고1 모의고사'!K14</f>
+        <v>69</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <f aca="false">'고2 모의고사'!C13</f>
+        <v>77</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <f aca="false">D15-B15</f>
         <v>15</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">'고1 모의고사'!B14</f>
-        <v>65.6</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <f aca="false">'고1 모의고사'!H14</f>
-        <v>75.5333333333333</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">'고2 모의고사'!C13</f>
-        <v>82</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <f aca="false">D14-B14</f>
-        <v>16.4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>16</v>
+      <c r="A16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <f aca="false">'고1 모의고사'!B15</f>
+        <v>65</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <f aca="false">'고1 모의고사'!K15</f>
+        <v>75.25</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">'고2 모의고사'!C14</f>
+        <v>81.1666666666667</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <f aca="false">D16-B16</f>
+        <v>16.1666666666667</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6038,21 +6823,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6062,10 +6847,13 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6075,10 +6863,13 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6088,10 +6879,13 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6101,254 +6895,366 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>63</v>
       </c>
       <c r="C9" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">B9</f>
         <v>63</v>
       </c>
-      <c r="F9" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B9:D9)</f>
+      <c r="I9" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B9:G9)</f>
         <v>75</v>
       </c>
-      <c r="G9" s="14" t="n">
-        <f aca="false">F9-E9</f>
+      <c r="J9" s="14" t="n">
+        <f aca="false">I9-H9</f>
         <v>12</v>
       </c>
-      <c r="H9" s="15" t="n">
-        <f aca="false">AVERAGE(B9:D9)</f>
-        <v>68</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <f aca="false">MAX(B9:D9)</f>
+      <c r="K9" s="15" t="n">
+        <f aca="false">AVERAGE(B9:G9)</f>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <f aca="false">MAX(B9:G9)</f>
         <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>59</v>
       </c>
       <c r="C10" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">B10</f>
         <v>59</v>
       </c>
-      <c r="F10" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B10:D10)</f>
+      <c r="I10" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B10:G10)</f>
         <v>73</v>
       </c>
-      <c r="G10" s="14" t="n">
-        <f aca="false">F10-E10</f>
+      <c r="J10" s="14" t="n">
+        <f aca="false">I10-H10</f>
         <v>14</v>
       </c>
-      <c r="H10" s="15" t="n">
-        <f aca="false">AVERAGE(B10:D10)</f>
-        <v>73</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <f aca="false">MAX(B10:D10)</f>
+      <c r="K10" s="15" t="n">
+        <f aca="false">AVERAGE(B10:G10)</f>
+        <v>76.5</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <f aca="false">MAX(B10:G10)</f>
         <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>88</v>
       </c>
       <c r="C11" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">B11</f>
         <v>88</v>
       </c>
-      <c r="F11" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B11:D11)</f>
+      <c r="I11" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B11:G11)</f>
         <v>100</v>
       </c>
-      <c r="G11" s="14" t="n">
-        <f aca="false">F11-E11</f>
+      <c r="J11" s="14" t="n">
+        <f aca="false">I11-H11</f>
         <v>12</v>
       </c>
-      <c r="H11" s="15" t="n">
-        <f aca="false">AVERAGE(B11:D11)</f>
-        <v>91.6666666666667</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <f aca="false">MAX(B11:D11)</f>
+      <c r="K11" s="15" t="n">
+        <f aca="false">AVERAGE(B11:G11)</f>
+        <v>92.3333333333333</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <f aca="false">MAX(B11:G11)</f>
         <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>67</v>
       </c>
       <c r="C12" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <f aca="false">B12</f>
         <v>67</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B12:D12)</f>
+      <c r="I12" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B12:G12)</f>
         <v>74</v>
       </c>
-      <c r="G12" s="14" t="n">
-        <f aca="false">F12-E12</f>
+      <c r="J12" s="14" t="n">
+        <f aca="false">I12-H12</f>
         <v>7</v>
       </c>
-      <c r="H12" s="15" t="n">
-        <f aca="false">AVERAGE(B12:D12)</f>
-        <v>76.3333333333333</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <f aca="false">MAX(B12:D12)</f>
-        <v>88</v>
+      <c r="K12" s="15" t="n">
+        <f aca="false">AVERAGE(B12:G12)</f>
+        <v>77.5</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <f aca="false">MAX(B12:G12)</f>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>51</v>
       </c>
       <c r="C13" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <f aca="false">B13</f>
         <v>51</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B13:D13)</f>
+      <c r="I13" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B13:G13)</f>
         <v>82</v>
       </c>
-      <c r="G13" s="14" t="n">
-        <f aca="false">F13-E13</f>
+      <c r="J13" s="14" t="n">
+        <f aca="false">I13-H13</f>
         <v>31</v>
       </c>
-      <c r="H13" s="15" t="n">
-        <f aca="false">AVERAGE(B13:D13)</f>
-        <v>68.6666666666667</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <f aca="false">MAX(B13:D13)</f>
-        <v>82</v>
+      <c r="K13" s="15" t="n">
+        <f aca="false">AVERAGE(B13:G13)</f>
+        <v>69.5</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <f aca="false">MAX(B13:G13)</f>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="16" t="n">
-        <f aca="false">AVERAGE(B9:B13)</f>
-        <v>65.6</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <f aca="false">AVERAGE(C9:C13)</f>
-        <v>80.2</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <f aca="false">AVERAGE(D9:D13)</f>
-        <v>80.8</v>
-      </c>
-      <c r="E14" s="16" t="n">
+      <c r="A14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H14" s="13" t="n">
         <f aca="false">B14</f>
-        <v>65.6</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <f aca="false">D14</f>
-        <v>80.8</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <f aca="false">F14-E14</f>
-        <v>15.2</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <f aca="false">AVERAGE(B9:D13)</f>
-        <v>75.5333333333333</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <f aca="false">MAX(B14:D14)</f>
-        <v>80.8</v>
+        <v>62</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B14:G14)</f>
+        <v>71</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <f aca="false">I14-H14</f>
+        <v>9</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <f aca="false">AVERAGE(B14:G14)</f>
+        <v>69</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <f aca="false">MAX(B14:G14)</f>
+        <v>78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>30</v>
+      <c r="A15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <f aca="false">AVERAGE(B9:B14)</f>
+        <v>65</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">AVERAGE(C9:C14)</f>
+        <v>73.1666666666667</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">AVERAGE(D9:D14)</f>
+        <v>73.8333333333333</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <f aca="false">AVERAGE(E9:E14)</f>
+        <v>81.3333333333333</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <f aca="false">AVERAGE(F9:F14)</f>
+        <v>79</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <f aca="false">AVERAGE(G9:G14)</f>
+        <v>79.1666666666667</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <f aca="false">B15</f>
+        <v>65</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <f aca="false">G15</f>
+        <v>79.1666666666667</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <f aca="false">I15-H15</f>
+        <v>14.1666666666667</v>
+      </c>
+      <c r="K15" s="16" t="n">
+        <f aca="false">AVERAGE(B9:G14)</f>
+        <v>75.25</v>
+      </c>
+      <c r="L15" s="16" t="n">
+        <f aca="false">MAX(B15:G15)</f>
+        <v>81.3333333333333</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6366,7 +7272,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6375,12 +7281,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6392,7 +7298,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6404,7 +7310,7 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -6416,18 +7322,18 @@
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>77</v>
@@ -6439,7 +7345,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>76</v>
@@ -6451,7 +7357,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>95</v>
@@ -6463,7 +7369,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>82</v>
@@ -6475,7 +7381,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>80</v>
@@ -6486,21 +7392,33 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="16" t="n">
-        <f aca="false">AVERAGE(B8:B12)</f>
-        <v>82</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <f aca="false">AVERAGE(B8:B12)</f>
-        <v>82</v>
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">AVERAGE(B13:B13)</f>
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>30</v>
+      <c r="A14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">AVERAGE(B8:B13)</f>
+        <v>81.1666666666667</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">AVERAGE(B8:B13)</f>
+        <v>81.1666666666667</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/isabel-cohorts/이서연반_총점_성장.xlsx
+++ b/output/isabel-cohorts/이서연반_총점_성장.xlsx
@@ -3269,11 +3269,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="90456211"/>
-        <c:axId val="23811808"/>
+        <c:axId val="49759322"/>
+        <c:axId val="448924"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90456211"/>
+        <c:axId val="49759322"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3305,7 +3305,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23811808"/>
+        <c:crossAx val="448924"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3313,7 +3313,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23811808"/>
+        <c:axId val="448924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3357,7 +3357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90456211"/>
+        <c:crossAx val="49759322"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3755,11 +3755,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5857185"/>
-        <c:axId val="14135670"/>
+        <c:axId val="22617632"/>
+        <c:axId val="15472346"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5857185"/>
+        <c:axId val="22617632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3791,7 +3791,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14135670"/>
+        <c:crossAx val="15472346"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3799,7 +3799,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14135670"/>
+        <c:axId val="15472346"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3843,7 +3843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5857185"/>
+        <c:crossAx val="22617632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4792,11 +4792,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="67900880"/>
-        <c:axId val="73448983"/>
+        <c:axId val="37767486"/>
+        <c:axId val="44581388"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67900880"/>
+        <c:axId val="37767486"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4828,7 +4828,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73448983"/>
+        <c:crossAx val="44581388"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4836,7 +4836,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73448983"/>
+        <c:axId val="44581388"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4914,7 +4914,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67900880"/>
+        <c:crossAx val="37767486"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -5238,11 +5238,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24695097"/>
-        <c:axId val="44001125"/>
+        <c:axId val="53361457"/>
+        <c:axId val="82123598"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24695097"/>
+        <c:axId val="53361457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5274,7 +5274,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44001125"/>
+        <c:crossAx val="82123598"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5282,7 +5282,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44001125"/>
+        <c:axId val="82123598"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5326,7 +5326,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24695097"/>
+        <c:crossAx val="53361457"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6030,11 +6030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="86492067"/>
-        <c:axId val="68043246"/>
+        <c:axId val="9094238"/>
+        <c:axId val="46372517"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="86492067"/>
+        <c:axId val="9094238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6066,7 +6066,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68043246"/>
+        <c:crossAx val="46372517"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6074,7 +6074,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68043246"/>
+        <c:axId val="46372517"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6152,7 +6152,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86492067"/>
+        <c:crossAx val="9094238"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>

--- a/output/isabel-cohorts/이서연반_총점_성장.xlsx
+++ b/output/isabel-cohorts/이서연반_총점_성장.xlsx
@@ -3269,11 +3269,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49759322"/>
-        <c:axId val="448924"/>
+        <c:axId val="57211330"/>
+        <c:axId val="21249971"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49759322"/>
+        <c:axId val="57211330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3305,7 +3305,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448924"/>
+        <c:crossAx val="21249971"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3313,7 +3313,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="448924"/>
+        <c:axId val="21249971"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3357,7 +3357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49759322"/>
+        <c:crossAx val="57211330"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3755,11 +3755,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22617632"/>
-        <c:axId val="15472346"/>
+        <c:axId val="73760035"/>
+        <c:axId val="44702247"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22617632"/>
+        <c:axId val="73760035"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3791,7 +3791,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15472346"/>
+        <c:crossAx val="44702247"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3799,7 +3799,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15472346"/>
+        <c:axId val="44702247"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3843,7 +3843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22617632"/>
+        <c:crossAx val="73760035"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4792,11 +4792,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="37767486"/>
-        <c:axId val="44581388"/>
+        <c:axId val="44443144"/>
+        <c:axId val="13131832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37767486"/>
+        <c:axId val="44443144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4828,7 +4828,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44581388"/>
+        <c:crossAx val="13131832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4836,7 +4836,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44581388"/>
+        <c:axId val="13131832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4914,7 +4914,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37767486"/>
+        <c:crossAx val="44443144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -5238,11 +5238,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="53361457"/>
-        <c:axId val="82123598"/>
+        <c:axId val="48588718"/>
+        <c:axId val="35282240"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53361457"/>
+        <c:axId val="48588718"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5274,7 +5274,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82123598"/>
+        <c:crossAx val="35282240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5282,7 +5282,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82123598"/>
+        <c:axId val="35282240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5326,7 +5326,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53361457"/>
+        <c:crossAx val="48588718"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6030,11 +6030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="9094238"/>
-        <c:axId val="46372517"/>
+        <c:axId val="52561700"/>
+        <c:axId val="21893409"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="9094238"/>
+        <c:axId val="52561700"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6066,7 +6066,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46372517"/>
+        <c:crossAx val="21893409"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6074,7 +6074,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46372517"/>
+        <c:axId val="21893409"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6152,7 +6152,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9094238"/>
+        <c:crossAx val="52561700"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>

--- a/output/isabel-cohorts/이서연반_총점_성장.xlsx
+++ b/output/isabel-cohorts/이서연반_총점_성장.xlsx
@@ -86,32 +86,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">으</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 어려워지는데도</t>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">순서로 어려워지는데도</t>
     </r>
     <r>
       <rPr>
@@ -3269,11 +3252,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57211330"/>
-        <c:axId val="21249971"/>
+        <c:axId val="63610513"/>
+        <c:axId val="58910724"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57211330"/>
+        <c:axId val="63610513"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3305,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21249971"/>
+        <c:crossAx val="58910724"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3313,7 +3296,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21249971"/>
+        <c:axId val="58910724"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3357,7 +3340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57211330"/>
+        <c:crossAx val="63610513"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3755,11 +3738,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="73760035"/>
-        <c:axId val="44702247"/>
+        <c:axId val="44798319"/>
+        <c:axId val="75800362"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73760035"/>
+        <c:axId val="44798319"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3791,7 +3774,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44702247"/>
+        <c:crossAx val="75800362"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3799,7 +3782,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44702247"/>
+        <c:axId val="75800362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3843,7 +3826,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73760035"/>
+        <c:crossAx val="44798319"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4792,11 +4775,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="44443144"/>
-        <c:axId val="13131832"/>
+        <c:axId val="8038909"/>
+        <c:axId val="45348399"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="44443144"/>
+        <c:axId val="8038909"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4828,7 +4811,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13131832"/>
+        <c:crossAx val="45348399"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4836,7 +4819,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13131832"/>
+        <c:axId val="45348399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4914,7 +4897,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44443144"/>
+        <c:crossAx val="8038909"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -5238,11 +5221,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="48588718"/>
-        <c:axId val="35282240"/>
+        <c:axId val="46264756"/>
+        <c:axId val="22245575"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48588718"/>
+        <c:axId val="46264756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5274,7 +5257,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35282240"/>
+        <c:crossAx val="22245575"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5282,7 +5265,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35282240"/>
+        <c:axId val="22245575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5326,7 +5309,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48588718"/>
+        <c:crossAx val="46264756"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6030,11 +6013,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="52561700"/>
-        <c:axId val="21893409"/>
+        <c:axId val="15621447"/>
+        <c:axId val="52896463"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52561700"/>
+        <c:axId val="15621447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6066,7 +6049,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21893409"/>
+        <c:crossAx val="52896463"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6074,7 +6057,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21893409"/>
+        <c:axId val="52896463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6152,7 +6135,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52561700"/>
+        <c:crossAx val="15621447"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
